--- a/scripts/exemplo-import-alunos.xlsx
+++ b/scripts/exemplo-import-alunos.xlsx
@@ -397,17 +397,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>nome</v>
+        <v>Nome</v>
       </c>
       <c r="B1" t="str">
-        <v>telefone</v>
+        <v>Telefone</v>
       </c>
       <c r="C1" t="str">
-        <v>plano</v>
+        <v>Plano</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Gênero</v>
       </c>
     </row>
     <row r="2">
@@ -420,6 +423,9 @@
       <c r="C2" t="str">
         <v>Elite</v>
       </c>
+      <c r="D2" t="str">
+        <v>M</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -431,6 +437,9 @@
       <c r="C3" t="str">
         <v>Convencional</v>
       </c>
+      <c r="D3" t="str">
+        <v>F</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -442,6 +451,9 @@
       <c r="C4" t="str">
         <v>Elite</v>
       </c>
+      <c r="D4" t="str">
+        <v>F</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -453,6 +465,9 @@
       <c r="C5" t="str">
         <v>Elite</v>
       </c>
+      <c r="D5" t="str">
+        <v>M</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -464,6 +479,9 @@
       <c r="C6" t="str">
         <v>Convencional</v>
       </c>
+      <c r="D6" t="str">
+        <v>F</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -475,6 +493,9 @@
       <c r="C7" t="str">
         <v>Elite</v>
       </c>
+      <c r="D7" t="str">
+        <v>M</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -486,6 +507,9 @@
       <c r="C8" t="str">
         <v>Premium</v>
       </c>
+      <c r="D8" t="str">
+        <v>F</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -497,6 +521,9 @@
       <c r="C9" t="str">
         <v>Convencional</v>
       </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -508,6 +535,9 @@
       <c r="C10" t="str">
         <v>Elite</v>
       </c>
+      <c r="D10" t="str">
+        <v>F</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -519,10 +549,13 @@
       <c r="C11" t="str">
         <v>Convencional</v>
       </c>
+      <c r="D11" t="str">
+        <v>M</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
   </ignoredErrors>
 </worksheet>
 </file>